--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\LevelUpEnergy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28DE9918-FFD3-457C-B0C7-D571A75D1A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6058619D-64D0-4944-85B6-3C1DB719855E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{B5F6F223-C8AB-4FE3-AABF-B83CDDD9790F}"/>
   </bookViews>
@@ -22,6 +22,23 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t>▶</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↔</t>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -649,6 +666,1003 @@
             </a:rPr>
             <a:t>分</a:t>
           </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>222250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>102216</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>76380</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF7EB616-BD53-3B95-CBA9-29288131737D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="14812309"/>
+          <a:ext cx="11935628" cy="3559542"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>194236</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>321236</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>194235</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{844BCE51-8ABB-CBB7-1A7D-469448FBC9C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6297706" y="18952883"/>
+          <a:ext cx="1255059" cy="463176"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>⛄</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>H.K</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>　🌙</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Y.K</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>372036</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>46319</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>312272</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>46318</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D783E7CD-396F-4574-B5E6-8A5666118E18}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6288742" y="14867966"/>
+          <a:ext cx="1255059" cy="463176"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Segoe Script" panose="030B0504020000000003" pitchFamily="66" charset="0"/>
+            </a:rPr>
+            <a:t>🌙</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>372036</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>170330</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>312272</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>170330</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="正方形/長方形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C715770A-79A8-4A64-82A7-635CE4E3A811}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6288742" y="19623742"/>
+          <a:ext cx="1255059" cy="463176"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>🌙</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Y.K</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>113554</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>46319</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>53790</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>46318</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05413631-8BF5-4328-84F3-CE1D0AC2F367}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11946966" y="14867966"/>
+          <a:ext cx="1255059" cy="463176"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>🌙</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Y.K</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>97118</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>547314</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>146930</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A304F38-23BD-0F15-8193-18F403EA9652}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="20013706"/>
+          <a:ext cx="9093667" cy="2597283"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>97117</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>22411</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>112058</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>134470</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="正方形/長方形 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{257E53B3-E8C5-8E25-D4D5-01F55B21D89A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2069352" y="20633764"/>
+          <a:ext cx="1987177" cy="343647"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>残：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>時間</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>15111</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>11314</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="図 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{402182D3-47C8-102E-156A-7078D22901B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="657412" y="23861059"/>
+          <a:ext cx="3302170" cy="2095608"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>369045</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>40340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>383987</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>152398</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="正方形/長方形 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{853F79E7-C85C-410F-B18D-416EBE04744B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1683869" y="24364575"/>
+          <a:ext cx="1987177" cy="343647"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>所要時間：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>30</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>119529</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>89647</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>218992</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>11658</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="図 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1550AF3F-EDD8-4349-B130-8AC58502B47A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="119529" y="27192941"/>
+          <a:ext cx="9303228" cy="1543129"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>298824</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>134471</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>164353</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="正方形/長方形 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6775EC86-CF39-E949-BDDD-05E3A26C52E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7530353" y="27237765"/>
+          <a:ext cx="1837765" cy="836706"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>635002</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>194234</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>116991</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>112078</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="図 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1F9C12F-73CA-AB0A-FB96-E53AB3BE3092}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7866531" y="27992293"/>
+          <a:ext cx="1454225" cy="381020"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>575236</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>209177</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>642471</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>71811</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="図 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27329A48-2350-7CCB-2E7A-C5BC013EF4BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7149354" y="28007236"/>
+          <a:ext cx="724646" cy="325810"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>74706</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>112164</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>224119</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="図 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFE75FC5-9C63-2246-6A6E-929800916320}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:srcRect b="67418"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="30188647"/>
+          <a:ext cx="9315929" cy="844178"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>32870</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>493059</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>119529</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="正方形/長方形 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F7A401E-F8AA-4BBB-908B-41AFA16A0EDD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7510929" y="30609988"/>
+          <a:ext cx="1528483" cy="318247"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -957,9 +1971,22 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="F101:H138"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData/>
+  <sheetData>
+    <row r="101" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="138" spans="6:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="F138" t="s">
+        <v>0</v>
+      </c>
+      <c r="G138" t="s">
+        <v>2</v>
+      </c>
+      <c r="H138" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
